--- a/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67660_completo.xlsx
+++ b/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67660_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc6f2b64f789e47a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6ed69d1477f745ab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.6281</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.7891</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.3781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.0317</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.7911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.9353</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.9728</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.5532</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67660_completo.xlsx
+++ b/1394_Cuenca_Tumbes/_raw_reportes_xlsx/IDConfig_67660_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6ed69d1477f745ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb0a3aeeedb704cdc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,486 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    103.4976</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    147.4612</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.1793</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.8250</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.2111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     24.1635</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     26.2814</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     25.7434</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.3743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     28.4899</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9292</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.2950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.5812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.8964</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.5812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.2328</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.2058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9292</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.9292</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.0562</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.0562</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -309,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     35.0317</x:v>
+        <x:v>     30.7891</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,13 +849,418 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>     37.5812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.6605</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.7891</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.7891</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.7891</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.3781</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.9728</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.9728</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     31.9728</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.1793</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.1793</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.5732</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.7911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.7911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.7911</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.4085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.4085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.9353</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.2950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.6605</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.5812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.9353</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.5532</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>     38.8902</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>15/08/2026</x:t>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.8902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.5812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.2625</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.6514</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -390,307 +1275,22 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>14/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     36.2950</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.7891</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     30.7891</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.3781</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.9728</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.9728</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     31.9728</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     33.1793</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     33.1793</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     32.5732</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     33.7911</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     33.7911</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     33.7911</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     34.4085</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     34.4085</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     36.9353</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     36.2950</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     35.6605</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     37.5812</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     36.9353</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/07/2026</x:t>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.2220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -705,52 +1305,97 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>24/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     38.8902</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     38.8902</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     37.5812</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
+          <x:t>16/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.5532</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.5532</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.8964</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.8964</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.5766</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.5766</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -765,7 +1410,37 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>20/07/2026</x:t>
+          <x:t>09/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.2625</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.9541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -780,22 +1455,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     39.5532</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
+          <x:t>06/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -810,172 +1470,52 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>17/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     39.5532</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>16/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     46.4979</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     39.5532</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     40.8964</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     40.8964</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     41.5766</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     41.5766</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     42.2625</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     42.2625</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     42.9541</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>07/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     43.6514</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/07/2026</x:t>
+          <x:t>05/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.2238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     64.9049</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.7777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/07/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -990,22 +1530,367 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>05/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     47.2238</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/07/2026</x:t>
+          <x:t>01/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     47.9554</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.7777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.4359</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.9393</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.1824</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.0150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.0150</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.6183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.5872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.6183</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     63.9233</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.3819</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.8006</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.4418</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.1060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.2710</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.2710</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     66.8937</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.9749</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.9416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     70.9749</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.2862</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    182.0544</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     81.7882</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1020,247 +1905,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>03/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     45.7777</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     45.0632</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     51.6996</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     49.4359</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     61.2710</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     56.3819</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     57.1824</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     54.0150</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     54.0150</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     59.6183</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     55.5872</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     59.6183</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     63.9233</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     56.3819</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     58.8006</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     60.4418</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>17/06/2026</x:t>
+          <x:t>06/06/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1275,67 +1920,82 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>16/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     61.2710</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>15/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     61.2710</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>14/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     66.8937</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>13/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     70.9749</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/06/2026</x:t>
+          <x:t>05/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.9503</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     64.9049</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.8950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     65.8950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     68.9170</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1350,52 +2010,67 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>11/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     70.9749</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>    125.2862</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>09/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>    182.0544</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>08/06/2026</x:t>
+          <x:t>30/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.9416</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.1950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.1950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.1950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1410,187 +2085,22 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>07/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     64.9049</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>06/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     62.1060</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>05/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     62.9467</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>04/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     64.9049</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>03/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     65.8950</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>02/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     65.8950</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>01/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     68.9170</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>31/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     69.9416</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>30/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     69.9416</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     75.1950</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     75.1950</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     75.1950</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/05/2026</x:t>
+          <x:t>25/05/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.6673</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1605,22 +2115,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>25/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     80.6673</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/05/2026</x:t>
+          <x:t>23/05/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -1635,21 +2130,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>23/05/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>     81.7882</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>22/05/2026</x:t>
         </x:is>
       </x:c>
@@ -1944,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    138.5990</x:v>
+        <x:v>    138.4144</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1420.0516</x:v>
+        <x:v>    103.4976</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>   1748.1682</x:v>
+        <x:v>    112.7372</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    603.2335</x:v>
+        <x:v>    158.1432</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    606.0560</x:v>
+        <x:v>    148.7764</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    328.1234</x:v>
+        <x:v>    155.4384</x:v>
       </x:c>
     </x:row>
     <x:row>
